--- a/resource/cell_state_annotation.xlsx
+++ b/resource/cell_state_annotation.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yhao/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yunhao/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4B5357-1B83-C740-9015-F313411FA536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440063BA-4F67-5542-9B7F-21CCA13D55BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17420" xr2:uid="{69795A8D-6EE6-9B47-B317-94FD4D1A71AB}"/>
+    <workbookView xWindow="1100" yWindow="760" windowWidth="28040" windowHeight="17420" activeTab="2" xr2:uid="{69795A8D-6EE6-9B47-B317-94FD4D1A71AB}"/>
   </bookViews>
   <sheets>
     <sheet name="cell_state_early_fetal" sheetId="2" r:id="rId1"/>
     <sheet name="cell_state_mid_fetal_to_adult" sheetId="1" r:id="rId2"/>
+    <sheet name="brain_region_state" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3327" uniqueCount="1031">
   <si>
     <t>cell_type</t>
   </si>
@@ -2541,9 +2542,6 @@
     <t>mode_proportion: proportion of cells in each state that belong to its most most prevalent stage</t>
   </si>
   <si>
-    <t>This spreadsheet contains the annotations of 82 cell states from mid fetal to adult (original dataset from: https://doi.org/10.1016/j.cell.2022.09.039)</t>
-  </si>
-  <si>
     <t>cell_type:  cell tpye of the state.  For detailed info about each cell type, please check Method section of the paper</t>
   </si>
   <si>
@@ -2569,13 +2567,577 @@
   </si>
   <si>
     <t>mean_stage: the average age of cells in each state (age is grouped into three stages within early fetal: early, mid, late)</t>
+  </si>
+  <si>
+    <t>This spreadsheet contains the annotations of 82 prefrontal cortex cell states from mid fetal to adult (original dataset from: https://doi.org/10.1016/j.cell.2022.09.039)</t>
+  </si>
+  <si>
+    <t>Brain_region_state_id: Brain region state ID. The ID matches with the column name of Seal model prediction file</t>
+  </si>
+  <si>
+    <t>Stage: stage of development</t>
+  </si>
+  <si>
+    <t>Brain_region_abbreviation: abbreviation of the brain region (from BrainSpan/PsychENCODE)</t>
+  </si>
+  <si>
+    <t>Brain_region_name: full name of the brain region</t>
+  </si>
+  <si>
+    <t>Brain_region_state_id</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>Brain_region_abbreviation</t>
+  </si>
+  <si>
+    <t>Brain_region_name</t>
+  </si>
+  <si>
+    <t>early_fetal.A1C</t>
+  </si>
+  <si>
+    <t>early_fetal</t>
+  </si>
+  <si>
+    <t>A1C</t>
+  </si>
+  <si>
+    <t>Primary auditory (A1) cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.AMY</t>
+  </si>
+  <si>
+    <t>AMY</t>
+  </si>
+  <si>
+    <t>Amygdala</t>
+  </si>
+  <si>
+    <t>early_fetal.CBC</t>
+  </si>
+  <si>
+    <t>CBC</t>
+  </si>
+  <si>
+    <t>Cerebellar cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.CGE</t>
+  </si>
+  <si>
+    <t>CGE</t>
+  </si>
+  <si>
+    <t>Caudal ganglionic eminence</t>
+  </si>
+  <si>
+    <t>early_fetal.DFC</t>
+  </si>
+  <si>
+    <t>DFC</t>
+  </si>
+  <si>
+    <t>Dorsolateral prefrontal cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.DTH</t>
+  </si>
+  <si>
+    <t>DTH</t>
+  </si>
+  <si>
+    <t>Dorsal thalamus</t>
+  </si>
+  <si>
+    <t>early_fetal.HIP</t>
+  </si>
+  <si>
+    <t>HIP</t>
+  </si>
+  <si>
+    <t>early_fetal.IPC</t>
+  </si>
+  <si>
+    <t>IPC</t>
+  </si>
+  <si>
+    <t>Posterior inferior parietal cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.ITC</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>Inferior temporal cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.LGE</t>
+  </si>
+  <si>
+    <t>LGE</t>
+  </si>
+  <si>
+    <t>Lateral ganglionic eminence</t>
+  </si>
+  <si>
+    <t>early_fetal.M1C</t>
+  </si>
+  <si>
+    <t>M1C</t>
+  </si>
+  <si>
+    <t>Primary motor cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.M1CS1C</t>
+  </si>
+  <si>
+    <t>M1CS1C</t>
+  </si>
+  <si>
+    <t>Primary motor-somatosensory cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.MD</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>Mediodorsal nucleus of thalamus</t>
+  </si>
+  <si>
+    <t>early_fetal.MFC</t>
+  </si>
+  <si>
+    <t>MFC</t>
+  </si>
+  <si>
+    <t>Medial prefrontal cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.MGE</t>
+  </si>
+  <si>
+    <t>MGE</t>
+  </si>
+  <si>
+    <t>Medial ganglionic eminence</t>
+  </si>
+  <si>
+    <t>early_fetal.OC</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>Occipital cerebral wall</t>
+  </si>
+  <si>
+    <t>early_fetal.OFC</t>
+  </si>
+  <si>
+    <t>OFC</t>
+  </si>
+  <si>
+    <t>Orbital prefrontal cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.PC</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Parietal cerebral wall</t>
+  </si>
+  <si>
+    <t>early_fetal.S1C</t>
+  </si>
+  <si>
+    <t>S1C</t>
+  </si>
+  <si>
+    <t>Primary somatosensory cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.STC</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>Superior temporal cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.STR</t>
+  </si>
+  <si>
+    <t>STR</t>
+  </si>
+  <si>
+    <t>early_fetal.TC</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>Temporal cerebral wall</t>
+  </si>
+  <si>
+    <t>early_fetal.URL</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Upper (rostral) rhombic lip</t>
+  </si>
+  <si>
+    <t>early_fetal.V1C</t>
+  </si>
+  <si>
+    <t>V1C</t>
+  </si>
+  <si>
+    <t>Primary visual (V1) cortex</t>
+  </si>
+  <si>
+    <t>early_fetal.VFC</t>
+  </si>
+  <si>
+    <t>VFC</t>
+  </si>
+  <si>
+    <t>Ventrolateral prefrontal cortex</t>
+  </si>
+  <si>
+    <t>mid_fetal.A1C</t>
+  </si>
+  <si>
+    <t>mid_fetal</t>
+  </si>
+  <si>
+    <t>mid_fetal.AMY</t>
+  </si>
+  <si>
+    <t>mid_fetal.CBC</t>
+  </si>
+  <si>
+    <t>mid_fetal.DFC</t>
+  </si>
+  <si>
+    <t>mid_fetal.HIP</t>
+  </si>
+  <si>
+    <t>mid_fetal.IPC</t>
+  </si>
+  <si>
+    <t>mid_fetal.ITC</t>
+  </si>
+  <si>
+    <t>mid_fetal.M1C</t>
+  </si>
+  <si>
+    <t>mid_fetal.MD</t>
+  </si>
+  <si>
+    <t>mid_fetal.MFC</t>
+  </si>
+  <si>
+    <t>mid_fetal.MSC</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>mid_fetal.OFC</t>
+  </si>
+  <si>
+    <t>mid_fetal.S1C</t>
+  </si>
+  <si>
+    <t>mid_fetal.STC</t>
+  </si>
+  <si>
+    <t>mid_fetal.STR</t>
+  </si>
+  <si>
+    <t>mid_fetal.V1C</t>
+  </si>
+  <si>
+    <t>mid_fetal.VFC</t>
+  </si>
+  <si>
+    <t>late_fetal.A1C</t>
+  </si>
+  <si>
+    <t>late_fetal</t>
+  </si>
+  <si>
+    <t>late_fetal.AMY</t>
+  </si>
+  <si>
+    <t>late_fetal.CBC</t>
+  </si>
+  <si>
+    <t>late_fetal.DFC</t>
+  </si>
+  <si>
+    <t>late_fetal.HIP</t>
+  </si>
+  <si>
+    <t>late_fetal.IPC</t>
+  </si>
+  <si>
+    <t>late_fetal.ITC</t>
+  </si>
+  <si>
+    <t>late_fetal.M1C</t>
+  </si>
+  <si>
+    <t>late_fetal.MD</t>
+  </si>
+  <si>
+    <t>late_fetal.MFC</t>
+  </si>
+  <si>
+    <t>late_fetal.OFC</t>
+  </si>
+  <si>
+    <t>late_fetal.S1C</t>
+  </si>
+  <si>
+    <t>late_fetal.STC</t>
+  </si>
+  <si>
+    <t>late_fetal.STR</t>
+  </si>
+  <si>
+    <t>late_fetal.V1C</t>
+  </si>
+  <si>
+    <t>late_fetal.VFC</t>
+  </si>
+  <si>
+    <t>infancy.A1C</t>
+  </si>
+  <si>
+    <t>infancy</t>
+  </si>
+  <si>
+    <t>infancy.AMY</t>
+  </si>
+  <si>
+    <t>infancy.CBC</t>
+  </si>
+  <si>
+    <t>infancy.DFC</t>
+  </si>
+  <si>
+    <t>infancy.HIP</t>
+  </si>
+  <si>
+    <t>infancy.IPC</t>
+  </si>
+  <si>
+    <t>infancy.ITC</t>
+  </si>
+  <si>
+    <t>infancy.M1C</t>
+  </si>
+  <si>
+    <t>infancy.MD</t>
+  </si>
+  <si>
+    <t>infancy.MFC</t>
+  </si>
+  <si>
+    <t>infancy.OFC</t>
+  </si>
+  <si>
+    <t>infancy.S1C</t>
+  </si>
+  <si>
+    <t>infancy.STC</t>
+  </si>
+  <si>
+    <t>infancy.STR</t>
+  </si>
+  <si>
+    <t>infancy.V1C</t>
+  </si>
+  <si>
+    <t>infancy.VFC</t>
+  </si>
+  <si>
+    <t>childhood.A1C</t>
+  </si>
+  <si>
+    <t>childhood</t>
+  </si>
+  <si>
+    <t>childhood.AMY</t>
+  </si>
+  <si>
+    <t>childhood.CBC</t>
+  </si>
+  <si>
+    <t>childhood.DFC</t>
+  </si>
+  <si>
+    <t>childhood.HIP</t>
+  </si>
+  <si>
+    <t>childhood.IPC</t>
+  </si>
+  <si>
+    <t>childhood.ITC</t>
+  </si>
+  <si>
+    <t>childhood.M1C</t>
+  </si>
+  <si>
+    <t>childhood.MD</t>
+  </si>
+  <si>
+    <t>childhood.MFC</t>
+  </si>
+  <si>
+    <t>childhood.OFC</t>
+  </si>
+  <si>
+    <t>childhood.S1C</t>
+  </si>
+  <si>
+    <t>childhood.STC</t>
+  </si>
+  <si>
+    <t>childhood.STR</t>
+  </si>
+  <si>
+    <t>childhood.V1C</t>
+  </si>
+  <si>
+    <t>childhood.VFC</t>
+  </si>
+  <si>
+    <t>adolescence.A1C</t>
+  </si>
+  <si>
+    <t>adolescence</t>
+  </si>
+  <si>
+    <t>adolescence.AMY</t>
+  </si>
+  <si>
+    <t>adolescence.CBC</t>
+  </si>
+  <si>
+    <t>adolescence.DFC</t>
+  </si>
+  <si>
+    <t>adolescence.HIP</t>
+  </si>
+  <si>
+    <t>adolescence.IPC</t>
+  </si>
+  <si>
+    <t>adolescence.ITC</t>
+  </si>
+  <si>
+    <t>adolescence.M1C</t>
+  </si>
+  <si>
+    <t>adolescence.MD</t>
+  </si>
+  <si>
+    <t>adolescence.MFC</t>
+  </si>
+  <si>
+    <t>adolescence.OFC</t>
+  </si>
+  <si>
+    <t>adolescence.S1C</t>
+  </si>
+  <si>
+    <t>adolescence.STC</t>
+  </si>
+  <si>
+    <t>adolescence.STR</t>
+  </si>
+  <si>
+    <t>adolescence.V1C</t>
+  </si>
+  <si>
+    <t>adolescence.VFC</t>
+  </si>
+  <si>
+    <t>adulthood.A1C</t>
+  </si>
+  <si>
+    <t>adulthood</t>
+  </si>
+  <si>
+    <t>adulthood.AMY</t>
+  </si>
+  <si>
+    <t>adulthood.CBC</t>
+  </si>
+  <si>
+    <t>adulthood.DFC</t>
+  </si>
+  <si>
+    <t>adulthood.HIP</t>
+  </si>
+  <si>
+    <t>adulthood.IPC</t>
+  </si>
+  <si>
+    <t>adulthood.ITC</t>
+  </si>
+  <si>
+    <t>adulthood.M1C</t>
+  </si>
+  <si>
+    <t>adulthood.MD</t>
+  </si>
+  <si>
+    <t>adulthood.MFC</t>
+  </si>
+  <si>
+    <t>adulthood.OFC</t>
+  </si>
+  <si>
+    <t>adulthood.S1C</t>
+  </si>
+  <si>
+    <t>adulthood.STC</t>
+  </si>
+  <si>
+    <t>adulthood.STR</t>
+  </si>
+  <si>
+    <t>adulthood.V1C</t>
+  </si>
+  <si>
+    <t>adulthood.VFC</t>
+  </si>
+  <si>
+    <t>This spreadsheet contains the annotations of 122 brain region  states from early fetal to adult (original dataset from: https://doi.org/10.1126/science.aat8464)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2607,6 +3169,51 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1A1818"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2679,10 +3286,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2692,13 +3300,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2716,14 +3317,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
@@ -2734,17 +3347,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3077,7 +3701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A55F44B-221B-F048-A4A4-2C6C10AB6D57}">
-  <dimension ref="A1:J608"/>
+  <dimension ref="A1:H608"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
@@ -3087,103 +3711,93 @@
     <col min="7" max="7" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>837</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="3" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
         <v>838</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="3" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
-        <v>829</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="23"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
         <v>839</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="23"/>
-    </row>
-    <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
-        <v>840</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="23"/>
-    </row>
-    <row r="6" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="11"/>
+    </row>
+    <row r="6" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
         <v>830</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="23"/>
-    </row>
-    <row r="7" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>841</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
         <v>842</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="23"/>
-    </row>
-    <row r="8" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
-        <v>843</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="23"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="23"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>825</v>
       </c>
@@ -3200,10 +3814,10 @@
         <v>189</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>190</v>
       </c>
@@ -3223,7 +3837,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>194</v>
       </c>
@@ -3243,7 +3857,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>197</v>
       </c>
@@ -3263,7 +3877,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>199</v>
       </c>
@@ -3283,7 +3897,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>200</v>
       </c>
@@ -3303,7 +3917,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>201</v>
       </c>
@@ -15165,13 +15779,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15192,72 +15806,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="13" t="s">
+        <v>843</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
+        <v>829</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>836</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
         <v>834</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
-        <v>829</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>837</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
-        <v>835</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="7"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>830</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="7"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="4"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -15272,48 +15886,47 @@
       <c r="T6" s="3"/>
     </row>
     <row r="7" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>832</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="11"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>833</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="5"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="16" t="s">
         <v>831</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="12"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>836</v>
+      <c r="B11" s="6" t="s">
+        <v>835</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>0</v>
@@ -15332,1893 +15945,1895 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="5">
         <v>3538</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="5">
         <v>0.30384397964951898</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="5">
         <v>7289</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="5">
         <v>0.37618328988887301</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="5">
         <v>3783</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="5">
         <v>0.89505683320116303</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="5">
         <v>6180</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="5">
         <v>0.93025889967637498</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="5">
         <v>3118</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="5">
         <v>0.82617062219371395</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="5">
         <v>610</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="5">
         <v>0.98852459016393401</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="5">
         <v>431</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="5">
         <v>0.94199535962877001</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="5">
         <v>104</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="5">
         <v>0.99038461538461497</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="5">
         <v>988</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="5">
         <v>0.97672064777327905</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="5">
         <v>513</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="5">
         <v>0.296296296296296</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="5">
         <v>798</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="5">
         <v>0.31453634085213</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="5">
         <v>259</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="5">
         <v>0.26254826254826202</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="5">
         <v>676</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="5">
         <v>0.34171597633136003</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="5">
         <v>560</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="5">
         <v>0.64464285714285696</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="5">
         <v>1190</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="5">
         <v>0.44957983193277301</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="5">
         <v>934</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="5">
         <v>0.37687366167023501</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="5">
         <v>4139</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="5">
         <v>0.69171297414834498</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="5">
         <v>3662</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="5">
         <v>0.48880393227744401</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="5">
         <v>2982</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="5">
         <v>0.81790744466800802</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="5">
         <v>1923</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="5">
         <v>0.98075923036921397</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="5">
         <v>1525</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="5">
         <v>0.91672131147540903</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="5">
         <v>1123</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="5">
         <v>0.57969723953695396</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="5">
         <v>1029</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="5">
         <v>0.99514091350825995</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="5">
         <v>4352</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="5">
         <v>0.55997242647058798</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="5">
         <v>1641</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="5">
         <v>0.80134064594759202</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="5">
         <v>1940</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="5">
         <v>0.38092783505154598</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="5">
         <v>3441</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="5">
         <v>0.40162743388549799</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="5">
         <v>2291</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="5">
         <v>0.44391095591444701</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="5">
         <v>1098</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="5">
         <v>0.44899817850637502</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="5">
         <v>308</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="5">
         <v>0.68181818181818099</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G41" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="5">
         <v>4169</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="5">
         <v>0.56320460542096396</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="5">
         <v>3361</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="5">
         <v>0.99791728652186795</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="5">
         <v>1420</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="5">
         <v>0.51760563380281599</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="5">
         <v>490</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="5">
         <v>0.397959183673469</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="G45" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="5">
         <v>3090</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="5">
         <v>0.994498381877022</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="5">
         <v>2713</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="5">
         <v>0.57537781054183501</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="5">
         <v>1072</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="5">
         <v>0.28544776119402898</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="G48" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="5">
         <v>2467</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="5">
         <v>0.36805837049047402</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="G49" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="5">
         <v>2456</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="5">
         <v>0.28460912052117199</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="5">
         <v>2850</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="5">
         <v>0.991929824561403</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="G51" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="5">
         <v>837</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="5">
         <v>0.27479091995221</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G52" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="5">
         <v>1021</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="5">
         <v>0.86875612144955905</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="G53" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="5">
         <v>591</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="5">
         <v>0.983079526226734</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G54" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="5">
         <v>5049</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="5">
         <v>0.324222618340265</v>
       </c>
-      <c r="G55" s="8" t="s">
+      <c r="G55" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="5">
         <v>623</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="5">
         <v>0.651685393258427</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="G56" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="5">
         <v>9627</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="5">
         <v>0.370416536823517</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="G57" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="5">
         <v>1518</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="5">
         <v>0.60606060606060597</v>
       </c>
-      <c r="G58" s="8" t="s">
+      <c r="G58" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="5">
         <v>961</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="5">
         <v>0.37565036420395398</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="G59" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="5">
         <v>5215</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="5">
         <v>0.64832214765100604</v>
       </c>
-      <c r="G60" s="8" t="s">
+      <c r="G60" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="5">
         <v>4870</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="5">
         <v>0.48603696098562599</v>
       </c>
-      <c r="G61" s="8" t="s">
+      <c r="G61" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="5">
         <v>4315</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="5">
         <v>0.835225955967555</v>
       </c>
-      <c r="G62" s="8" t="s">
+      <c r="G62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="5">
         <v>1633</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="5">
         <v>0.657072872014696</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="G63" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="5">
         <v>843</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="5">
         <v>0.51364175563463799</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="G64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="5">
         <v>5603</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="5">
         <v>0.64697483490986896</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="G65" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="5">
         <v>3827</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F66" s="8">
+      <c r="F66" s="5">
         <v>0.99346746799059305</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="5">
         <v>792</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F67" s="8">
+      <c r="F67" s="5">
         <v>0.40656565656565602</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G67" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="5">
         <v>335</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="5">
         <v>0.25970149253731301</v>
       </c>
-      <c r="G68" s="8" t="s">
+      <c r="G68" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="5">
         <v>1709</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="5">
         <v>0.32241076653013401</v>
       </c>
-      <c r="G69" s="8" t="s">
+      <c r="G69" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="5">
         <v>1012</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F70" s="8">
+      <c r="F70" s="5">
         <v>0.60375494071146196</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="5">
         <v>682</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F71" s="8">
+      <c r="F71" s="5">
         <v>0.34897360703812302</v>
       </c>
-      <c r="G71" s="8" t="s">
+      <c r="G71" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="5">
         <v>305</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="5">
         <v>0.68196721311475395</v>
       </c>
-      <c r="G72" s="8" t="s">
+      <c r="G72" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="5">
         <v>410</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="5">
         <v>0.43170731707317</v>
       </c>
-      <c r="G73" s="8" t="s">
+      <c r="G73" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="5">
         <v>1115</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="5">
         <v>0.373094170403587</v>
       </c>
-      <c r="G74" s="8" t="s">
+      <c r="G74" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="5">
         <v>820</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E75" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="5">
         <v>0.39512195121951199</v>
       </c>
-      <c r="G75" s="8" t="s">
+      <c r="G75" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B76" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="5">
         <v>973</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E76" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F76" s="8">
+      <c r="F76" s="5">
         <v>0.279547790339157</v>
       </c>
-      <c r="G76" s="8" t="s">
+      <c r="G76" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="5">
         <v>406</v>
       </c>
-      <c r="E77" s="8" t="s">
+      <c r="E77" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="5">
         <v>0.30788177339901401</v>
       </c>
-      <c r="G77" s="8" t="s">
+      <c r="G77" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="5">
         <v>825</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F78" s="8">
+      <c r="F78" s="5">
         <v>0.38787878787878699</v>
       </c>
-      <c r="G78" s="8" t="s">
+      <c r="G78" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="5">
         <v>1673</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="E79" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F79" s="8">
+      <c r="F79" s="5">
         <v>0.40884638374178101</v>
       </c>
-      <c r="G79" s="8" t="s">
+      <c r="G79" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="5">
         <v>882</v>
       </c>
-      <c r="E80" s="8" t="s">
+      <c r="E80" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F80" s="8">
+      <c r="F80" s="5">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G80" s="8" t="s">
+      <c r="G80" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="5">
         <v>295</v>
       </c>
-      <c r="E81" s="8" t="s">
+      <c r="E81" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F81" s="8">
+      <c r="F81" s="5">
         <v>0.29491525423728798</v>
       </c>
-      <c r="G81" s="8" t="s">
+      <c r="G81" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="8" t="s">
+      <c r="A82" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="5">
         <v>817</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F82" s="8">
+      <c r="F82" s="5">
         <v>0.27050183598531202</v>
       </c>
-      <c r="G82" s="8" t="s">
+      <c r="G82" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D83" s="8">
+      <c r="D83" s="5">
         <v>705</v>
       </c>
-      <c r="E83" s="8" t="s">
+      <c r="E83" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="8">
+      <c r="F83" s="5">
         <v>0.33617021276595699</v>
       </c>
-      <c r="G83" s="8" t="s">
+      <c r="G83" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="8" t="s">
+      <c r="A84" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="5">
         <v>1314</v>
       </c>
-      <c r="E84" s="8" t="s">
+      <c r="E84" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F84" s="8">
+      <c r="F84" s="5">
         <v>0.34931506849315003</v>
       </c>
-      <c r="G84" s="8" t="s">
+      <c r="G84" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="5">
         <v>983</v>
       </c>
-      <c r="E85" s="8" t="s">
+      <c r="E85" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F85" s="8">
+      <c r="F85" s="5">
         <v>0.373346897253306</v>
       </c>
-      <c r="G85" s="8" t="s">
+      <c r="G85" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C86" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D86" s="8">
+      <c r="D86" s="5">
         <v>572</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E86" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="8">
+      <c r="F86" s="5">
         <v>0.37062937062937001</v>
       </c>
-      <c r="G86" s="8" t="s">
+      <c r="G86" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B87" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="5">
         <v>1364</v>
       </c>
-      <c r="E87" s="8" t="s">
+      <c r="E87" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F87" s="8">
+      <c r="F87" s="5">
         <v>0.364369501466275</v>
       </c>
-      <c r="G87" s="8" t="s">
+      <c r="G87" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="8" t="s">
+      <c r="A88" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C88" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D88" s="8">
+      <c r="D88" s="5">
         <v>770</v>
       </c>
-      <c r="E88" s="8" t="s">
+      <c r="E88" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F88" s="8">
+      <c r="F88" s="5">
         <v>0.27922077922077898</v>
       </c>
-      <c r="G88" s="8" t="s">
+      <c r="G88" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D89" s="8">
+      <c r="D89" s="5">
         <v>166</v>
       </c>
-      <c r="E89" s="8" t="s">
+      <c r="E89" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="8">
+      <c r="F89" s="5">
         <v>0.373493975903614</v>
       </c>
-      <c r="G89" s="8" t="s">
+      <c r="G89" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B90" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="5">
         <v>177</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F90" s="8">
+      <c r="F90" s="5">
         <v>0.870056497175141</v>
       </c>
-      <c r="G90" s="8" t="s">
+      <c r="G90" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="5">
         <v>190</v>
       </c>
-      <c r="E91" s="8" t="s">
+      <c r="E91" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F91" s="8">
+      <c r="F91" s="5">
         <v>0.41052631578947302</v>
       </c>
-      <c r="G91" s="8" t="s">
+      <c r="G91" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="5">
         <v>220</v>
       </c>
-      <c r="E92" s="8" t="s">
+      <c r="E92" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="8">
+      <c r="F92" s="5">
         <v>0.40909090909090901</v>
       </c>
-      <c r="G92" s="8" t="s">
+      <c r="G92" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B93" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="5">
         <v>813</v>
       </c>
-      <c r="E93" s="8" t="s">
+      <c r="E93" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F93" s="8">
+      <c r="F93" s="5">
         <v>0.56703567035670299</v>
       </c>
-      <c r="G93" s="8" t="s">
+      <c r="G93" s="5" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
@@ -17226,9 +17841,1939 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCABDD05-7BAB-1249-915D-DA57DA0ADF0B}">
+  <dimension ref="A1:G130"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="3" max="3" width="26.5" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="26" t="s">
+        <v>844</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="26" t="s">
+        <v>845</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="26" t="s">
+        <v>846</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="21" t="s">
+        <v>848</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>849</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>850</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>851</v>
+      </c>
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="22" t="s">
+        <v>852</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>854</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>855</v>
+      </c>
+      <c r="E9" s="20"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="22" t="s">
+        <v>856</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>857</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>858</v>
+      </c>
+      <c r="E10" s="20"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="22" t="s">
+        <v>859</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>860</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="22" t="s">
+        <v>862</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>863</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>864</v>
+      </c>
+      <c r="E12" s="20"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="22" t="s">
+        <v>865</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>866</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>867</v>
+      </c>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="22" t="s">
+        <v>868</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>869</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>870</v>
+      </c>
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="22" t="s">
+        <v>871</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="22" t="s">
+        <v>873</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>875</v>
+      </c>
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="22" t="s">
+        <v>876</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>877</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>878</v>
+      </c>
+      <c r="E17" s="20"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="22" t="s">
+        <v>879</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>880</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>881</v>
+      </c>
+      <c r="E18" s="20"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>882</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>883</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>884</v>
+      </c>
+      <c r="E19" s="20"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="22" t="s">
+        <v>885</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>886</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>887</v>
+      </c>
+      <c r="E20" s="20"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="25" t="s">
+        <v>888</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>889</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>890</v>
+      </c>
+      <c r="E21" s="20"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="22" t="s">
+        <v>891</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>893</v>
+      </c>
+      <c r="E22" s="20"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="22" t="s">
+        <v>894</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>895</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>896</v>
+      </c>
+      <c r="E23" s="20"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="22" t="s">
+        <v>897</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>898</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>899</v>
+      </c>
+      <c r="E24" s="20"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="22" t="s">
+        <v>900</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>902</v>
+      </c>
+      <c r="E25" s="20"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="22" t="s">
+        <v>903</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>904</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>905</v>
+      </c>
+      <c r="E26" s="20"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="22" t="s">
+        <v>906</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>907</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>908</v>
+      </c>
+      <c r="E27" s="20"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="22" t="s">
+        <v>909</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>910</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>911</v>
+      </c>
+      <c r="E28" s="20"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="22" t="s">
+        <v>912</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E29" s="20"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="25" t="s">
+        <v>914</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>915</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>916</v>
+      </c>
+      <c r="E30" s="20"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="22" t="s">
+        <v>917</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>918</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>919</v>
+      </c>
+      <c r="E31" s="20"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="22" t="s">
+        <v>920</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>921</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>922</v>
+      </c>
+      <c r="E32" s="20"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="22" t="s">
+        <v>923</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="E33" s="20"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="22" t="s">
+        <v>926</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>854</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>855</v>
+      </c>
+      <c r="E34" s="20"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="22" t="s">
+        <v>928</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>857</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>858</v>
+      </c>
+      <c r="E35" s="20"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="22" t="s">
+        <v>929</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>860</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E36" s="20"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="22" t="s">
+        <v>930</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>866</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>867</v>
+      </c>
+      <c r="E37" s="20"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="22" t="s">
+        <v>931</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E38" s="20"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="22" t="s">
+        <v>932</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>875</v>
+      </c>
+      <c r="E39" s="20"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="22" t="s">
+        <v>933</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>877</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>878</v>
+      </c>
+      <c r="E40" s="20"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="22" t="s">
+        <v>934</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>883</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>884</v>
+      </c>
+      <c r="E41" s="20"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="25" t="s">
+        <v>935</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>889</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>890</v>
+      </c>
+      <c r="E42" s="20"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="22" t="s">
+        <v>936</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>893</v>
+      </c>
+      <c r="E43" s="20"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="22" t="s">
+        <v>937</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>938</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>887</v>
+      </c>
+      <c r="E44" s="20"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="22" t="s">
+        <v>939</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>902</v>
+      </c>
+      <c r="E45" s="20"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="22" t="s">
+        <v>940</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>907</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>908</v>
+      </c>
+      <c r="E46" s="20"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="22" t="s">
+        <v>941</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>910</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>911</v>
+      </c>
+      <c r="E47" s="20"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="22" t="s">
+        <v>942</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E48" s="20"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="22" t="s">
+        <v>943</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>921</v>
+      </c>
+      <c r="D49" s="22" t="s">
+        <v>922</v>
+      </c>
+      <c r="E49" s="20"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="22" t="s">
+        <v>944</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="E50" s="20"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="22" t="s">
+        <v>945</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>854</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>855</v>
+      </c>
+      <c r="E51" s="20"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="22" t="s">
+        <v>947</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>857</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>858</v>
+      </c>
+      <c r="E52" s="20"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="22" t="s">
+        <v>948</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>860</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E53" s="20"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="22" t="s">
+        <v>949</v>
+      </c>
+      <c r="B54" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>866</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>867</v>
+      </c>
+      <c r="E54" s="20"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="22" t="s">
+        <v>950</v>
+      </c>
+      <c r="B55" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="D55" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E55" s="20"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="22" t="s">
+        <v>951</v>
+      </c>
+      <c r="B56" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C56" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>875</v>
+      </c>
+      <c r="E56" s="20"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="22" t="s">
+        <v>952</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>877</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>878</v>
+      </c>
+      <c r="E57" s="20"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="22" t="s">
+        <v>953</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>883</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>884</v>
+      </c>
+      <c r="E58" s="20"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="25" t="s">
+        <v>954</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>889</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>890</v>
+      </c>
+      <c r="E59" s="20"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="22" t="s">
+        <v>955</v>
+      </c>
+      <c r="B60" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>893</v>
+      </c>
+      <c r="E60" s="20"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="22" t="s">
+        <v>956</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>902</v>
+      </c>
+      <c r="E61" s="20"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="22" t="s">
+        <v>957</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>907</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>908</v>
+      </c>
+      <c r="E62" s="20"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="22" t="s">
+        <v>958</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>910</v>
+      </c>
+      <c r="D63" s="22" t="s">
+        <v>911</v>
+      </c>
+      <c r="E63" s="20"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="22" t="s">
+        <v>959</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="D64" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E64" s="20"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="22" t="s">
+        <v>960</v>
+      </c>
+      <c r="B65" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>921</v>
+      </c>
+      <c r="D65" s="22" t="s">
+        <v>922</v>
+      </c>
+      <c r="E65" s="20"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="22" t="s">
+        <v>961</v>
+      </c>
+      <c r="B66" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C66" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="D66" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="E66" s="20"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="22" t="s">
+        <v>962</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>854</v>
+      </c>
+      <c r="D67" s="23" t="s">
+        <v>855</v>
+      </c>
+      <c r="E67" s="20"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="22" t="s">
+        <v>964</v>
+      </c>
+      <c r="B68" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C68" s="22" t="s">
+        <v>857</v>
+      </c>
+      <c r="D68" s="22" t="s">
+        <v>858</v>
+      </c>
+      <c r="E68" s="20"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="B69" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>860</v>
+      </c>
+      <c r="D69" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E69" s="20"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="22" t="s">
+        <v>966</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>866</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>867</v>
+      </c>
+      <c r="E70" s="20"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="22" t="s">
+        <v>967</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C71" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="D71" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E71" s="20"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="22" t="s">
+        <v>968</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C72" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="D72" s="24" t="s">
+        <v>875</v>
+      </c>
+      <c r="E72" s="20"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C73" s="22" t="s">
+        <v>877</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>878</v>
+      </c>
+      <c r="E73" s="20"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="22" t="s">
+        <v>970</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C74" s="22" t="s">
+        <v>883</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>884</v>
+      </c>
+      <c r="E74" s="20"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="25" t="s">
+        <v>971</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>889</v>
+      </c>
+      <c r="D75" s="22" t="s">
+        <v>890</v>
+      </c>
+      <c r="E75" s="20"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="22" t="s">
+        <v>972</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C76" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="D76" s="22" t="s">
+        <v>893</v>
+      </c>
+      <c r="E76" s="20"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="22" t="s">
+        <v>973</v>
+      </c>
+      <c r="B77" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C77" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="D77" s="22" t="s">
+        <v>902</v>
+      </c>
+      <c r="E77" s="20"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="22" t="s">
+        <v>974</v>
+      </c>
+      <c r="B78" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C78" s="22" t="s">
+        <v>907</v>
+      </c>
+      <c r="D78" s="22" t="s">
+        <v>908</v>
+      </c>
+      <c r="E78" s="20"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="22" t="s">
+        <v>975</v>
+      </c>
+      <c r="B79" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C79" s="22" t="s">
+        <v>910</v>
+      </c>
+      <c r="D79" s="22" t="s">
+        <v>911</v>
+      </c>
+      <c r="E79" s="20"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="22" t="s">
+        <v>976</v>
+      </c>
+      <c r="B80" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C80" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="D80" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E80" s="20"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="22" t="s">
+        <v>977</v>
+      </c>
+      <c r="B81" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C81" s="22" t="s">
+        <v>921</v>
+      </c>
+      <c r="D81" s="22" t="s">
+        <v>922</v>
+      </c>
+      <c r="E81" s="20"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="22" t="s">
+        <v>978</v>
+      </c>
+      <c r="B82" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="C82" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="D82" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="E82" s="20"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="22" t="s">
+        <v>979</v>
+      </c>
+      <c r="B83" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C83" s="22" t="s">
+        <v>854</v>
+      </c>
+      <c r="D83" s="23" t="s">
+        <v>855</v>
+      </c>
+      <c r="E83" s="20"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="22" t="s">
+        <v>981</v>
+      </c>
+      <c r="B84" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C84" s="22" t="s">
+        <v>857</v>
+      </c>
+      <c r="D84" s="22" t="s">
+        <v>858</v>
+      </c>
+      <c r="E84" s="20"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="22" t="s">
+        <v>982</v>
+      </c>
+      <c r="B85" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C85" s="22" t="s">
+        <v>860</v>
+      </c>
+      <c r="D85" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E85" s="20"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="22" t="s">
+        <v>983</v>
+      </c>
+      <c r="B86" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C86" s="22" t="s">
+        <v>866</v>
+      </c>
+      <c r="D86" s="24" t="s">
+        <v>867</v>
+      </c>
+      <c r="E86" s="20"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="22" t="s">
+        <v>984</v>
+      </c>
+      <c r="B87" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C87" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="D87" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E87" s="20"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="22" t="s">
+        <v>985</v>
+      </c>
+      <c r="B88" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C88" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="D88" s="24" t="s">
+        <v>875</v>
+      </c>
+      <c r="E88" s="20"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="22" t="s">
+        <v>986</v>
+      </c>
+      <c r="B89" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C89" s="22" t="s">
+        <v>877</v>
+      </c>
+      <c r="D89" s="22" t="s">
+        <v>878</v>
+      </c>
+      <c r="E89" s="20"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="22" t="s">
+        <v>987</v>
+      </c>
+      <c r="B90" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C90" s="22" t="s">
+        <v>883</v>
+      </c>
+      <c r="D90" s="22" t="s">
+        <v>884</v>
+      </c>
+      <c r="E90" s="20"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="25" t="s">
+        <v>988</v>
+      </c>
+      <c r="B91" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C91" s="22" t="s">
+        <v>889</v>
+      </c>
+      <c r="D91" s="22" t="s">
+        <v>890</v>
+      </c>
+      <c r="E91" s="20"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="22" t="s">
+        <v>989</v>
+      </c>
+      <c r="B92" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C92" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="D92" s="22" t="s">
+        <v>893</v>
+      </c>
+      <c r="E92" s="20"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" s="22" t="s">
+        <v>990</v>
+      </c>
+      <c r="B93" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C93" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="D93" s="22" t="s">
+        <v>902</v>
+      </c>
+      <c r="E93" s="20"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="22" t="s">
+        <v>991</v>
+      </c>
+      <c r="B94" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C94" s="22" t="s">
+        <v>907</v>
+      </c>
+      <c r="D94" s="22" t="s">
+        <v>908</v>
+      </c>
+      <c r="E94" s="20"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="22" t="s">
+        <v>992</v>
+      </c>
+      <c r="B95" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C95" s="22" t="s">
+        <v>910</v>
+      </c>
+      <c r="D95" s="22" t="s">
+        <v>911</v>
+      </c>
+      <c r="E95" s="20"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="22" t="s">
+        <v>993</v>
+      </c>
+      <c r="B96" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="D96" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E96" s="20"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="22" t="s">
+        <v>994</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>921</v>
+      </c>
+      <c r="D97" s="22" t="s">
+        <v>922</v>
+      </c>
+      <c r="E97" s="20"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="22" t="s">
+        <v>995</v>
+      </c>
+      <c r="B98" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="C98" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="D98" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="E98" s="20"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="22" t="s">
+        <v>996</v>
+      </c>
+      <c r="B99" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C99" s="22" t="s">
+        <v>854</v>
+      </c>
+      <c r="D99" s="23" t="s">
+        <v>855</v>
+      </c>
+      <c r="E99" s="20"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="22" t="s">
+        <v>998</v>
+      </c>
+      <c r="B100" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C100" s="22" t="s">
+        <v>857</v>
+      </c>
+      <c r="D100" s="22" t="s">
+        <v>858</v>
+      </c>
+      <c r="E100" s="20"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="22" t="s">
+        <v>999</v>
+      </c>
+      <c r="B101" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C101" s="22" t="s">
+        <v>860</v>
+      </c>
+      <c r="D101" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E101" s="20"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="22" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B102" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C102" s="22" t="s">
+        <v>866</v>
+      </c>
+      <c r="D102" s="24" t="s">
+        <v>867</v>
+      </c>
+      <c r="E102" s="20"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="22" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B103" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C103" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="D103" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E103" s="20"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="22" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B104" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C104" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="D104" s="24" t="s">
+        <v>875</v>
+      </c>
+      <c r="E104" s="20"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="22" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B105" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C105" s="22" t="s">
+        <v>877</v>
+      </c>
+      <c r="D105" s="22" t="s">
+        <v>878</v>
+      </c>
+      <c r="E105" s="20"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="22" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B106" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C106" s="22" t="s">
+        <v>883</v>
+      </c>
+      <c r="D106" s="22" t="s">
+        <v>884</v>
+      </c>
+      <c r="E106" s="20"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="25" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B107" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C107" s="22" t="s">
+        <v>889</v>
+      </c>
+      <c r="D107" s="22" t="s">
+        <v>890</v>
+      </c>
+      <c r="E107" s="20"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="22" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B108" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C108" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="D108" s="22" t="s">
+        <v>893</v>
+      </c>
+      <c r="E108" s="20"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="22" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B109" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C109" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="D109" s="22" t="s">
+        <v>902</v>
+      </c>
+      <c r="E109" s="20"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="22" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B110" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C110" s="22" t="s">
+        <v>907</v>
+      </c>
+      <c r="D110" s="22" t="s">
+        <v>908</v>
+      </c>
+      <c r="E110" s="20"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B111" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C111" s="22" t="s">
+        <v>910</v>
+      </c>
+      <c r="D111" s="22" t="s">
+        <v>911</v>
+      </c>
+      <c r="E111" s="20"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="22" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B112" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C112" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="D112" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E112" s="20"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="22" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B113" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C113" s="22" t="s">
+        <v>921</v>
+      </c>
+      <c r="D113" s="22" t="s">
+        <v>922</v>
+      </c>
+      <c r="E113" s="20"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="22" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B114" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="C114" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="D114" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="E114" s="20"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="22" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B115" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C115" s="22" t="s">
+        <v>854</v>
+      </c>
+      <c r="D115" s="23" t="s">
+        <v>855</v>
+      </c>
+      <c r="E115" s="20"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="22" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B116" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C116" s="22" t="s">
+        <v>857</v>
+      </c>
+      <c r="D116" s="22" t="s">
+        <v>858</v>
+      </c>
+      <c r="E116" s="20"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="22" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B117" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C117" s="22" t="s">
+        <v>860</v>
+      </c>
+      <c r="D117" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E117" s="20"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="22" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B118" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C118" s="22" t="s">
+        <v>866</v>
+      </c>
+      <c r="D118" s="24" t="s">
+        <v>867</v>
+      </c>
+      <c r="E118" s="20"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="22" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B119" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C119" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="D119" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E119" s="20"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" s="22" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B120" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C120" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="D120" s="24" t="s">
+        <v>875</v>
+      </c>
+      <c r="E120" s="20"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="22" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B121" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C121" s="22" t="s">
+        <v>877</v>
+      </c>
+      <c r="D121" s="22" t="s">
+        <v>878</v>
+      </c>
+      <c r="E121" s="20"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" s="22" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B122" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C122" s="22" t="s">
+        <v>883</v>
+      </c>
+      <c r="D122" s="22" t="s">
+        <v>884</v>
+      </c>
+      <c r="E122" s="20"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" s="25" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B123" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C123" s="22" t="s">
+        <v>889</v>
+      </c>
+      <c r="D123" s="22" t="s">
+        <v>890</v>
+      </c>
+      <c r="E123" s="20"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="22" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B124" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C124" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="D124" s="22" t="s">
+        <v>893</v>
+      </c>
+      <c r="E124" s="20"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="22" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B125" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C125" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="D125" s="22" t="s">
+        <v>902</v>
+      </c>
+      <c r="E125" s="20"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" s="22" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B126" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C126" s="22" t="s">
+        <v>907</v>
+      </c>
+      <c r="D126" s="22" t="s">
+        <v>908</v>
+      </c>
+      <c r="E126" s="20"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" s="22" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B127" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C127" s="22" t="s">
+        <v>910</v>
+      </c>
+      <c r="D127" s="22" t="s">
+        <v>911</v>
+      </c>
+      <c r="E127" s="20"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" s="22" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B128" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C128" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="D128" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E128" s="20"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" s="22" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B129" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C129" s="22" t="s">
+        <v>921</v>
+      </c>
+      <c r="D129" s="22" t="s">
+        <v>922</v>
+      </c>
+      <c r="E129" s="20"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" s="22" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B130" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C130" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="D130" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="E130" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A21" r:id="rId1" display="http://early_fetal.md/" xr:uid="{DF460C8F-FC7C-CB40-8656-251A8B1B8FB7}"/>
+    <hyperlink ref="A30" r:id="rId2" display="http://early_fetal.tc/" xr:uid="{25D1160C-2D4B-0B4D-959B-2213496F2162}"/>
+    <hyperlink ref="A42" r:id="rId3" display="http://mid_fetal.md/" xr:uid="{88EAE06F-3D19-4F46-B23E-A2981A64C1FA}"/>
+    <hyperlink ref="A59" r:id="rId4" display="http://late_fetal.md/" xr:uid="{F5C96559-B250-8642-AA95-21EC5AA5E2A9}"/>
+    <hyperlink ref="A75" r:id="rId5" display="http://infancy.md/" xr:uid="{E4A9722F-4CB7-0A49-A557-915D2877D526}"/>
+    <hyperlink ref="A91" r:id="rId6" display="http://childhood.md/" xr:uid="{238EF5C8-DAB8-E24D-9BDF-8D295EBB420D}"/>
+    <hyperlink ref="A107" r:id="rId7" display="http://adolescence.md/" xr:uid="{69088163-3AE6-7544-9BF9-EA2E64253219}"/>
+    <hyperlink ref="A123" r:id="rId8" display="http://adulthood.md/" xr:uid="{AF5D7B54-ED2D-4241-8183-831E81D050D4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>